--- a/LangConfig/JP.xlsx
+++ b/LangConfig/JP.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -565,15 +565,32 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>EnchantCount</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1回の舐めで行うエンチャント回数</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>舐めに成功するたびに行うエンチャント抽選の回数です。有効範囲は1～10で、同じエンチャントが選ばれた場合はレベルが加算されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>RequireLickAbility</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>エヘカトルの祝福を必要とする</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>有効にすると、現在のマップに「エヘカトルの祝福」特性を持つキャラクターが必要です。無効時はプレイヤーが関連効果を発動します。</t>
         </is>
